--- a/Result/profitability/2305.xlsx
+++ b/Result/profitability/2305.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02</v>
+        <v>0.065</v>
       </c>
       <c r="N2" t="n">
-        <v>41.805</v>
+        <v>42.825</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.15</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002500000000000002</v>
+        <v>0.05374999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>39.50375</v>
+        <v>40.07875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.11</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.003749999999999998</v>
+        <v>0.02874999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>36.7075</v>
+        <v>37.8875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.53</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.08125</v>
+        <v>-0.01250000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>33.58875</v>
+        <v>34.23125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.18</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.07875</v>
+        <v>-0.05125</v>
       </c>
       <c r="N6" t="n">
-        <v>31.505</v>
+        <v>31.99</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.41</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.14625</v>
+        <v>-0.125</v>
       </c>
       <c r="N7" t="n">
-        <v>28.0225</v>
+        <v>27.6225</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.205</v>
+        <v>-0.18125</v>
       </c>
       <c r="N8" t="n">
-        <v>25.21125</v>
+        <v>25.92</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2305</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>386</v>
+      </c>
+      <c r="D75" t="n">
+        <v>201</v>
+      </c>
+      <c r="E75" t="n">
+        <v>185</v>
+      </c>
+      <c r="F75" t="n">
+        <v>47.88</v>
+      </c>
+      <c r="G75" t="n">
+        <v>91</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>23.57%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>47</v>
+      </c>
+      <c r="J75" t="n">
+        <v>138</v>
+      </c>
+      <c r="K75" t="n">
+        <v>71</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.07999999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>43.66875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.670000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1343283582089552</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.140000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1202620496022462</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
